--- a/DAV-Trier_Eingabeformular_Touren.xlsx
+++ b/DAV-Trier_Eingabeformular_Touren.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Berenike\DAV360_Transformator\dummy_daten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C69F80-D253-4165-8346-25698E06156C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86AA7E3B-15CB-4661-9EBD-0076C6A45196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="64">
   <si>
     <t>ID</t>
   </si>
@@ -168,9 +168,6 @@
     <t xml:space="preserve">Brenta, wie auf dem Mond </t>
   </si>
   <si>
-    <t>1000</t>
-  </si>
-  <si>
     <t>12</t>
   </si>
   <si>
@@ -214,13 +211,20 @@
   </si>
   <si>
     <t>Bergsteigen</t>
+  </si>
+  <si>
+    <t>1000-1200</t>
+  </si>
+  <si>
+    <t>Preis</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
   </numFmts>
@@ -253,11 +257,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -358,15 +363,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AC3" totalsRowShown="0">
-  <autoFilter ref="A1:AC3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC3">
-    <sortCondition ref="P1:P3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AD3" totalsRowShown="0">
+  <autoFilter ref="A1:AD3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD3">
+    <sortCondition ref="Q1:Q3"/>
   </sortState>
-  <tableColumns count="29">
+  <tableColumns count="30">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="26"/>
     <tableColumn id="28" xr3:uid="{5CD9351B-7746-48F9-B249-84C2C4B99709}" name="Lfd-Nr."/>
     <tableColumn id="29" xr3:uid="{34AA66A1-7F37-4DCB-BBF0-A1E019B30938}" name="Gruppen"/>
+    <tableColumn id="30" xr3:uid="{FFCDCC42-695B-489C-8724-FD71A2DADFD8}" name="Preis"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Startzeit" dataDxfId="25"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Fertigstellungszeit" dataDxfId="24"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="E-Mail" dataDxfId="23"/>
@@ -695,263 +701,272 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="20" customWidth="1"/>
-    <col min="4" max="29" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="20" customWidth="1"/>
+    <col min="5" max="30" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>15</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>18</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>19</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>20</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="4">
+        <v>300</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46136.5180555556</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46136.519780092603</v>
+      </c>
+      <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="1">
-        <v>46136.5180555556</v>
-      </c>
-      <c r="E2" s="1">
-        <v>46136.519780092603</v>
-      </c>
-      <c r="F2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="Q2" s="2">
+        <v>46143</v>
+      </c>
+      <c r="R2" s="2">
+        <v>46151</v>
+      </c>
+      <c r="S2" t="s">
         <v>49</v>
       </c>
-      <c r="P2" s="2">
+      <c r="T2" t="s">
+        <v>50</v>
+      </c>
+      <c r="U2" t="s">
+        <v>51</v>
+      </c>
+      <c r="V2" t="s">
+        <v>52</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="X2" s="2">
         <v>46143</v>
       </c>
-      <c r="Q2" s="2">
-        <v>46151</v>
-      </c>
-      <c r="R2" t="s">
-        <v>50</v>
-      </c>
-      <c r="S2" t="s">
-        <v>51</v>
-      </c>
-      <c r="T2" t="s">
-        <v>52</v>
-      </c>
-      <c r="U2" t="s">
-        <v>53</v>
-      </c>
-      <c r="V2" s="3" t="s">
+      <c r="Y2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="W2" s="2">
-        <v>46143</v>
-      </c>
-      <c r="X2" s="3" t="s">
+      <c r="Z2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB2" t="s">
         <v>55</v>
       </c>
-      <c r="Y2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA2" t="s">
+      <c r="AC2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD2" t="s">
         <v>56</v>
       </c>
-      <c r="AB2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>57</v>
-      </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="1">
+        <v>61</v>
+      </c>
+      <c r="D3" s="4">
+        <v>600</v>
+      </c>
+      <c r="E3" s="1">
         <v>46134.753506944398</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F3" s="1">
         <v>46134.758101851803</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" t="s">
+      <c r="I3" s="1"/>
+      <c r="J3" t="s">
         <v>28</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>29</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>30</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>34</v>
       </c>
-      <c r="P3" s="2">
+      <c r="Q3" s="2">
         <v>46423</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="R3" s="2">
         <v>46439</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>35</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>36</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>37</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="W3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="W3" s="2"/>
-      <c r="X3" t="s">
+      <c r="X3" s="2"/>
+      <c r="Y3" t="s">
         <v>39</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>40</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AA3" t="s">
         <v>41</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>42</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AC3" t="s">
         <v>43</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AD3" t="s">
         <v>44</v>
       </c>
     </row>
